--- a/excel_routes/route_LXR_JED_threats.xlsx
+++ b/excel_routes/route_LXR_JED_threats.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_260726_at_14.46\reports\excel_routes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_270726_at_12.25\reports\excel_routes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5DFF8BA-5195-461E-BE3F-AD2ADCE8AA74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76C215F2-FF37-4656-9F31-467247D9942A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12972" yWindow="348" windowWidth="10068" windowHeight="10284" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="34">
   <si>
     <t>Date</t>
   </si>
@@ -60,43 +60,31 @@
     <t>Currency</t>
   </si>
   <si>
-    <t>08-AUG-26</t>
+    <t>19-AUG-26</t>
+  </si>
+  <si>
+    <t>SM-987</t>
+  </si>
+  <si>
+    <t>Nesma Airlines NE-500</t>
+  </si>
+  <si>
+    <t>MED</t>
+  </si>
+  <si>
+    <t>EGP</t>
+  </si>
+  <si>
+    <t>26-AUG-26</t>
+  </si>
+  <si>
+    <t>02-SEP-26</t>
+  </si>
+  <si>
+    <t>05-SEP-26</t>
   </si>
   <si>
     <t>SM-989</t>
-  </si>
-  <si>
-    <t>Nesma Airlines NE-500</t>
-  </si>
-  <si>
-    <t>MED</t>
-  </si>
-  <si>
-    <t>EGP</t>
-  </si>
-  <si>
-    <t>15-AUG-26</t>
-  </si>
-  <si>
-    <t>19-AUG-26</t>
-  </si>
-  <si>
-    <t>SM-987</t>
-  </si>
-  <si>
-    <t>22-AUG-26</t>
-  </si>
-  <si>
-    <t>26-AUG-26</t>
-  </si>
-  <si>
-    <t>29-AUG-26</t>
-  </si>
-  <si>
-    <t>02-SEP-26</t>
-  </si>
-  <si>
-    <t>05-SEP-26</t>
   </si>
   <si>
     <t>09-SEP-26</t>
@@ -526,7 +514,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -590,10 +578,10 @@
         <v>19727</v>
       </c>
       <c r="E2" s="2">
-        <v>24260</v>
+        <v>24259</v>
       </c>
       <c r="F2" s="2">
-        <v>-4533</v>
+        <v>-4532</v>
       </c>
       <c r="G2" s="2">
         <v>30</v>
@@ -625,10 +613,10 @@
         <v>19727</v>
       </c>
       <c r="E3" s="2">
-        <v>24260</v>
+        <v>24259</v>
       </c>
       <c r="F3" s="2">
-        <v>-4533</v>
+        <v>-4532</v>
       </c>
       <c r="G3" s="2">
         <v>30</v>
@@ -651,7 +639,7 @@
         <v>17</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>13</v>
@@ -660,10 +648,10 @@
         <v>19727</v>
       </c>
       <c r="E4" s="2">
-        <v>24260</v>
+        <v>24259</v>
       </c>
       <c r="F4" s="2">
-        <v>-4533</v>
+        <v>-4532</v>
       </c>
       <c r="G4" s="2">
         <v>30</v>
@@ -683,11 +671,11 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="C5" s="2" t="s">
         <v>13</v>
       </c>
@@ -695,10 +683,10 @@
         <v>19727</v>
       </c>
       <c r="E5" s="2">
-        <v>24260</v>
+        <v>24259</v>
       </c>
       <c r="F5" s="2">
-        <v>-4533</v>
+        <v>-4532</v>
       </c>
       <c r="G5" s="2">
         <v>30</v>
@@ -721,7 +709,7 @@
         <v>20</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>13</v>
@@ -730,10 +718,10 @@
         <v>19727</v>
       </c>
       <c r="E6" s="2">
-        <v>24260</v>
+        <v>24259</v>
       </c>
       <c r="F6" s="2">
-        <v>-4533</v>
+        <v>-4532</v>
       </c>
       <c r="G6" s="2">
         <v>30</v>
@@ -756,7 +744,7 @@
         <v>21</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>13</v>
@@ -765,10 +753,10 @@
         <v>19727</v>
       </c>
       <c r="E7" s="2">
-        <v>24260</v>
+        <v>24259</v>
       </c>
       <c r="F7" s="2">
-        <v>-4533</v>
+        <v>-4532</v>
       </c>
       <c r="G7" s="2">
         <v>30</v>
@@ -791,7 +779,7 @@
         <v>22</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>13</v>
@@ -800,10 +788,10 @@
         <v>19727</v>
       </c>
       <c r="E8" s="2">
-        <v>24260</v>
+        <v>24259</v>
       </c>
       <c r="F8" s="2">
-        <v>-4533</v>
+        <v>-4532</v>
       </c>
       <c r="G8" s="2">
         <v>30</v>
@@ -826,7 +814,7 @@
         <v>23</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>13</v>
@@ -835,10 +823,10 @@
         <v>19727</v>
       </c>
       <c r="E9" s="2">
-        <v>24260</v>
+        <v>24259</v>
       </c>
       <c r="F9" s="2">
-        <v>-4533</v>
+        <v>-4532</v>
       </c>
       <c r="G9" s="2">
         <v>30</v>
@@ -861,7 +849,7 @@
         <v>24</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>13</v>
@@ -870,10 +858,10 @@
         <v>19727</v>
       </c>
       <c r="E10" s="2">
-        <v>24260</v>
+        <v>24259</v>
       </c>
       <c r="F10" s="2">
-        <v>-4533</v>
+        <v>-4532</v>
       </c>
       <c r="G10" s="2">
         <v>30</v>
@@ -896,7 +884,7 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>13</v>
@@ -905,10 +893,10 @@
         <v>19727</v>
       </c>
       <c r="E11" s="2">
-        <v>24260</v>
+        <v>24259</v>
       </c>
       <c r="F11" s="2">
-        <v>-4533</v>
+        <v>-4532</v>
       </c>
       <c r="G11" s="2">
         <v>30</v>
@@ -931,7 +919,7 @@
         <v>26</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>13</v>
@@ -940,10 +928,10 @@
         <v>19727</v>
       </c>
       <c r="E12" s="2">
-        <v>24260</v>
+        <v>24259</v>
       </c>
       <c r="F12" s="2">
-        <v>-4533</v>
+        <v>-4532</v>
       </c>
       <c r="G12" s="2">
         <v>30</v>
@@ -966,7 +954,7 @@
         <v>27</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>13</v>
@@ -975,10 +963,10 @@
         <v>19727</v>
       </c>
       <c r="E13" s="2">
-        <v>24260</v>
+        <v>24259</v>
       </c>
       <c r="F13" s="2">
-        <v>-4533</v>
+        <v>-4532</v>
       </c>
       <c r="G13" s="2">
         <v>30</v>
@@ -1001,7 +989,7 @@
         <v>28</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>13</v>
@@ -1010,10 +998,10 @@
         <v>19727</v>
       </c>
       <c r="E14" s="2">
-        <v>24260</v>
+        <v>24259</v>
       </c>
       <c r="F14" s="2">
-        <v>-4533</v>
+        <v>-4532</v>
       </c>
       <c r="G14" s="2">
         <v>30</v>
@@ -1036,7 +1024,7 @@
         <v>29</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>13</v>
@@ -1045,10 +1033,10 @@
         <v>19727</v>
       </c>
       <c r="E15" s="2">
-        <v>24260</v>
+        <v>24259</v>
       </c>
       <c r="F15" s="2">
-        <v>-4533</v>
+        <v>-4532</v>
       </c>
       <c r="G15" s="2">
         <v>30</v>
@@ -1071,7 +1059,7 @@
         <v>30</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>13</v>
@@ -1080,10 +1068,10 @@
         <v>19727</v>
       </c>
       <c r="E16" s="2">
-        <v>24260</v>
+        <v>24259</v>
       </c>
       <c r="F16" s="2">
-        <v>-4533</v>
+        <v>-4532</v>
       </c>
       <c r="G16" s="2">
         <v>30</v>
@@ -1106,7 +1094,7 @@
         <v>31</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>13</v>
@@ -1115,10 +1103,10 @@
         <v>19727</v>
       </c>
       <c r="E17" s="2">
-        <v>24260</v>
+        <v>24259</v>
       </c>
       <c r="F17" s="2">
-        <v>-4533</v>
+        <v>-4532</v>
       </c>
       <c r="G17" s="2">
         <v>30</v>
@@ -1141,7 +1129,7 @@
         <v>32</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>13</v>
@@ -1150,10 +1138,10 @@
         <v>19727</v>
       </c>
       <c r="E18" s="2">
-        <v>24260</v>
+        <v>24259</v>
       </c>
       <c r="F18" s="2">
-        <v>-4533</v>
+        <v>-4532</v>
       </c>
       <c r="G18" s="2">
         <v>30</v>
@@ -1176,7 +1164,7 @@
         <v>33</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>13</v>
@@ -1185,10 +1173,10 @@
         <v>19727</v>
       </c>
       <c r="E19" s="2">
-        <v>24260</v>
+        <v>24259</v>
       </c>
       <c r="F19" s="2">
-        <v>-4533</v>
+        <v>-4532</v>
       </c>
       <c r="G19" s="2">
         <v>30</v>
@@ -1203,146 +1191,6 @@
         <v>14</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D20" s="2">
-        <v>19727</v>
-      </c>
-      <c r="E20" s="2">
-        <v>24260</v>
-      </c>
-      <c r="F20" s="2">
-        <v>-4533</v>
-      </c>
-      <c r="G20" s="2">
-        <v>30</v>
-      </c>
-      <c r="H20" s="2">
-        <v>30</v>
-      </c>
-      <c r="I20" s="2">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D21" s="2">
-        <v>19727</v>
-      </c>
-      <c r="E21" s="2">
-        <v>24260</v>
-      </c>
-      <c r="F21" s="2">
-        <v>-4533</v>
-      </c>
-      <c r="G21" s="2">
-        <v>30</v>
-      </c>
-      <c r="H21" s="2">
-        <v>30</v>
-      </c>
-      <c r="I21" s="2">
-        <v>0</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D22" s="2">
-        <v>19727</v>
-      </c>
-      <c r="E22" s="2">
-        <v>24260</v>
-      </c>
-      <c r="F22" s="2">
-        <v>-4533</v>
-      </c>
-      <c r="G22" s="2">
-        <v>30</v>
-      </c>
-      <c r="H22" s="2">
-        <v>30</v>
-      </c>
-      <c r="I22" s="2">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D23" s="2">
-        <v>19727</v>
-      </c>
-      <c r="E23" s="2">
-        <v>24260</v>
-      </c>
-      <c r="F23" s="2">
-        <v>-4533</v>
-      </c>
-      <c r="G23" s="2">
-        <v>30</v>
-      </c>
-      <c r="H23" s="2">
-        <v>30</v>
-      </c>
-      <c r="I23" s="2">
-        <v>0</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K23" s="2" t="s">
         <v>15</v>
       </c>
     </row>
